--- a/templates/assets/visa-list-template.xlsx
+++ b/templates/assets/visa-list-template.xlsx
@@ -856,64 +856,41 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF339966"/>
       <name val="Times New Roman"/>
